--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,35 +441,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>phone</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>علی مصاحب طلب</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>9144415789</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>سمیرا</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>9144415789</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>visit_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>doctor</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fee</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,81 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>fee</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>visit_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>زهرا</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>45</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9144415789</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>حجامت</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>مینا</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>04433665565</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>زالو</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2 عدد زالو از پاها</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="patients" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="visits" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="income" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,7 +27,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <color rgb="FF0F1115"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,26 +49,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -147,44 +143,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -211,14 +207,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -245,6 +259,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -256,166 +288,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -425,53 +433,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>age</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>phone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>disease</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>visit_date</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>doctor</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>fee</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>visit_note</t>
+          <t xml:space="preserve">created_at </t>
         </is>
       </c>
     </row>
@@ -481,71 +469,190 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>زهرا</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>45</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9144415789</v>
+          <t>مهدی</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>091</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>حجامت</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>1405/04/04 23:16</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.42578125" customWidth="1" min="2" max="2"/>
+    <col width="13.42578125" customWidth="1" min="3" max="3"/>
+    <col width="14.140625" customWidth="1" min="4" max="5"/>
+    <col width="15.28515625" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_id </t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">visit_date </t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reason </t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>treatment</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost </t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created_at </t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1405-04-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>حجامت</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>600000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>حجامت عام</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1405/04/04 23:17</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>مینا</t>
-        </is>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>1405/04/01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>04433665565</t>
+          <t>حجامت</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>زالو</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>400000</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2 عدد زالو از پاها</t>
+          <t>حجامت عام</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1405/04/04 23:17</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.28515625" customWidth="1" min="2" max="2"/>
+    <col width="14.42578125" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.25" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patient_id </t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">date </t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">description </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,41 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel-webapp\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3806A4-A3B1-4F8B-A06A-7C2745AA3599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="patients" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="visits" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="income" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="patients" sheetId="1" r:id="rId1"/>
+    <sheet name="visits" sheetId="2" r:id="rId2"/>
+    <sheet name="income" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>created_at </t>
+  </si>
+  <si>
+    <t>patient_id </t>
+  </si>
+  <si>
+    <t>visit_date </t>
+  </si>
+  <si>
+    <t>reason </t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>cost </t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>date </t>
+  </si>
+  <si>
+    <t>description </t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <family val="2"/>
-      <color rgb="FF0F1115"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -54,81 +103,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -428,64 +418,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">created_at </t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>مهدی</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>091</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>حجامت</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1405/04/04 23:16</t>
-        </is>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -494,117 +445,37 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="12.42578125" customWidth="1" min="2" max="2"/>
-    <col width="13.42578125" customWidth="1" min="3" max="3"/>
-    <col width="14.140625" customWidth="1" min="4" max="5"/>
-    <col width="15.28515625" customWidth="1" min="7" max="7"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="5" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_id </t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">visit_date </t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reason </t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cost </t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">created_at </t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1405-04-01</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>حجامت</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>حجامت عام</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1405/04/04 23:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1405/04/01</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>حجامت</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>حجامت عام</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1405/04/04 23:17</t>
-        </is>
+    <row r="1" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -613,43 +484,29 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="16.28515625" customWidth="1" min="2" max="2"/>
-    <col width="14.42578125" customWidth="1" min="5" max="5"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patient_id </t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">date </t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">description </t>
-        </is>
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
